--- a/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED22.xlsx
+++ b/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED22.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-09T17:31:57+08:00</t>
+          <t>2026-08-09T17:48:53+08:00</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>229W</t>
+          <t>89W</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -831,7 +831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N3"/>
+  <dimension ref="B2:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -917,6 +917,18 @@
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>贷款时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1季</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>74W</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1584,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ready</t>
+          <t>busy</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1700,7 +1712,7 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED-2-0068</t>
+          <t>SIM_XA_FIXED-3-0141</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1714,11 +1726,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>77W</t>
+          <t>39W</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1728,17 +1740,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>第2年</t>
+          <t>第3年</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5季</t>
+          <t>4季</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2季</t>
+          <t>1季</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1748,14 +1760,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年2季</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED-4-0022</t>
+          <t>SIM_XA_FIXED-4-0024</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1769,11 +1781,11 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>42W</t>
+          <t>74W</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1788,12 +1800,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4季</t>
+          <t>5季</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4季</t>
+          <t>2季</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1803,7 +1815,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年3季</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G52"/>
+  <dimension ref="B2:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -1945,7 +1957,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>production_line_ordered | {"line": {"accumulated_depreciation_wan": 40.0, "book_value_wan": 0.0, "cost_wan": 40.0, "line_id": "L-b022bf23be", "line_type": "手工线", "maintenance_wan_per_year": 15.0, "ownership": "purchased", "product_id": "P1", "remaining_install_quarters": 0, "status": "ready"}}</t>
+          <t>production_line_ordered | {"line": {"accumulated_depreciation_wan": 40.0, "book_value_wan": 0.0, "cost_wan": 40.0, "line_id": "L-b022bf23be", "line_type": "手工线", "maintenance_wan_per_year": 15.0, "ownership": "purchased", "product_id": "P1", "remaining_install_quarters": 0, "status": "busy"}}</t>
         </is>
       </c>
     </row>
@@ -2397,14 +2409,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-24</v>
+        <v>-14</v>
       </c>
       <c r="E24" t="n">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2413,7 +2425,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 24.0, "material_id": "R1", "quantity": 2.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2423,23 +2435,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-16</v>
+        <v>-14</v>
       </c>
       <c r="E25" t="n">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 40.0, "job_id": "JOB-1e2561e5f4", "line_id": "L-b022bf23be", "product_id": "P1", "quantity": 2.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2449,23 +2461,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="E26" t="n">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
         </is>
       </c>
     </row>
@@ -2475,23 +2487,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="E27" t="n">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-09f619d139", "line_id": "L-b022bf23be", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2501,14 +2513,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E28" t="n">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2517,7 +2529,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 40.0, "order_id": "SIM_XA_FIXED-2-0068", "receivable_term_quarters": 2, "revenue_wan": 77.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2527,14 +2539,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-24</v>
+        <v>-15</v>
       </c>
       <c r="E29" t="n">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2543,7 +2555,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 24.0, "material_id": "R1", "quantity": 2.0}</t>
+          <t>maintenance_expense | {"line_id": "L-b022bf23be"}</t>
         </is>
       </c>
     </row>
@@ -2553,14 +2565,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>283</v>
+        <v>314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2569,7 +2581,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 40.0, "job_id": "JOB-09f619d139", "line_id": "L-b022bf23be", "product_id": "P1", "quantity": 2.0, "remaining_quarters": 0}}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-b022bf23be", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2579,14 +2591,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>269</v>
+        <v>314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2595,7 +2607,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-b022bf23be", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2605,23 +2617,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-15</v>
+        <v>-8</v>
       </c>
       <c r="E32" t="n">
-        <v>254</v>
+        <v>306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-b022bf23be"}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2631,23 +2643,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E33" t="n">
-        <v>254</v>
+        <v>292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-b022bf23be", "asset_type": "factory"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2657,23 +2669,23 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>254</v>
+        <v>292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-b022bf23be", "asset_type": "production_line"}</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 20.0, "order_id": "SIM_XA_FIXED-3-0141", "receivable_term_quarters": 1, "revenue_wan": 39.0}</t>
         </is>
       </c>
     </row>
@@ -2683,23 +2695,23 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="E35" t="n">
-        <v>246</v>
+        <v>280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
         </is>
       </c>
     </row>
@@ -2709,23 +2721,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="E36" t="n">
-        <v>232</v>
+        <v>272</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-4d40ae31dd", "line_id": "L-b022bf23be", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2735,23 +2747,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Update_Receivable</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>77</v>
+        <v>-14</v>
       </c>
       <c r="E37" t="n">
-        <v>309</v>
+        <v>258</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>receivable_collected | {"receivable_id": "AR-8da95ba1e3"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2761,14 +2773,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Update_Receivable</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-14</v>
+        <v>39</v>
       </c>
       <c r="E38" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2777,7 +2789,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>receivable_collected | {"receivable_id": "AR-71954e7d7f"}</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2806,7 @@
         <v>-14</v>
       </c>
       <c r="E39" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2813,14 +2825,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E40" t="n">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2829,7 +2841,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 20.0, "order_id": "SIM_XA_FIXED-4-0022", "receivable_term_quarters": 4, "revenue_wan": 42.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2839,14 +2851,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="E41" t="n">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2855,7 +2867,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>maintenance_expense | {"line_id": "L-b022bf23be"}</t>
         </is>
       </c>
     </row>
@@ -2865,14 +2877,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2881,7 +2893,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-b022bf23be"}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-b022bf23be", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2910,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2907,7 +2919,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-b022bf23be", "asset_type": "factory"}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-b022bf23be", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2917,23 +2929,23 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="E44" t="n">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-b022bf23be", "asset_type": "production_line"}</t>
+          <t>emergency_material_purchase | {"cost_wan": 24.0, "material_id": "R1", "quantity": 2.0}</t>
         </is>
       </c>
     </row>
@@ -2943,14 +2955,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>-8</v>
+        <v>-16</v>
       </c>
       <c r="E45" t="n">
-        <v>244</v>
+        <v>214</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2959,7 +2971,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 40.0, "job_id": "JOB-94fd15e344", "line_id": "L-b022bf23be", "product_id": "P1", "quantity": 2.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2969,14 +2981,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="E46" t="n">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2985,7 +2997,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
         </is>
       </c>
     </row>
@@ -3002,11 +3014,11 @@
         <v>-14</v>
       </c>
       <c r="E47" t="n">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>第5年2季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3028,11 +3040,11 @@
         <v>-14</v>
       </c>
       <c r="E48" t="n">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>第5年3季</t>
+          <t>第5年2季</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3047,14 +3059,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Update_Receivable</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>244</v>
+        <v>178</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3063,7 +3075,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>receivable_collected | {"receivable_id": "AR-6e348c61d4"}</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 60.0, "order_id": "SIM_XA_FIXED-4-0024", "receivable_term_quarters": 2, "revenue_wan": 74.0}</t>
         </is>
       </c>
     </row>
@@ -3073,23 +3085,23 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-15</v>
+        <v>-36</v>
       </c>
       <c r="E50" t="n">
-        <v>229</v>
+        <v>142</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>第5年4季</t>
+          <t>第5年3季</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-b022bf23be"}</t>
+          <t>emergency_material_purchase | {"cost_wan": 36.0, "material_id": "R1", "quantity": 3.0}</t>
         </is>
       </c>
     </row>
@@ -3099,23 +3111,23 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="E51" t="n">
-        <v>229</v>
+        <v>118</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>第5年4季</t>
+          <t>第5年3季</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-b022bf23be", "asset_type": "factory"}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 60.0, "job_id": "JOB-a8ee27829d", "line_id": "L-b022bf23be", "product_id": "P1", "quantity": 3.0, "remaining_quarters": 1}}</t>
         </is>
       </c>
     </row>
@@ -3125,21 +3137,99 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
+          <t>Pay_Overhaul</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>-14</v>
+      </c>
+      <c r="E52" t="n">
+        <v>104</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>第5年3季</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>management_fee_expense</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="n">
+        <v>50</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Pay_Maintenance</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>-15</v>
+      </c>
+      <c r="E53" t="n">
+        <v>89</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>第5年4季</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>maintenance_expense | {"line_id": "L-b022bf23be"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="n">
+        <v>51</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
           <t>Depreciation</t>
         </is>
       </c>
-      <c r="D52" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" t="n">
-        <v>229</v>
-      </c>
-      <c r="F52" t="inlineStr">
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>89</v>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>第5年4季</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-b022bf23be", "asset_type": "factory"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="n">
+        <v>52</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>89</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>第5年4季</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
         <is>
           <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-b022bf23be", "asset_type": "production_line"}</t>
         </is>
@@ -3536,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -3561,13 +3651,13 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>20</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
@@ -3586,13 +3676,13 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -3636,13 +3726,13 @@
         <v>-79</v>
       </c>
       <c r="F20" t="n">
-        <v>-42</v>
+        <v>-79</v>
       </c>
       <c r="G20" t="n">
-        <v>-57</v>
+        <v>-60</v>
       </c>
       <c r="H20" t="n">
-        <v>-65</v>
+        <v>-51</v>
       </c>
     </row>
     <row r="21">
@@ -3686,13 +3776,13 @@
         <v>-94.2</v>
       </c>
       <c r="F22" t="n">
-        <v>-57.2</v>
+        <v>-94.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-72.2</v>
+        <v>-75.2</v>
       </c>
       <c r="H22" t="n">
-        <v>-80.2</v>
+        <v>-66.2</v>
       </c>
     </row>
     <row r="23">
@@ -3736,13 +3826,13 @@
         <v>-94.2</v>
       </c>
       <c r="F24" t="n">
-        <v>-57.2</v>
+        <v>-94.2</v>
       </c>
       <c r="G24" t="n">
-        <v>-72.2</v>
+        <v>-75.2</v>
       </c>
       <c r="H24" t="n">
-        <v>-80.2</v>
+        <v>-66.2</v>
       </c>
     </row>
     <row r="25">
@@ -3786,13 +3876,13 @@
         <v>-94.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-57.2</v>
+        <v>-94.2</v>
       </c>
       <c r="G26" t="n">
-        <v>-72.2</v>
+        <v>-75.2</v>
       </c>
       <c r="H26" t="n">
-        <v>-80.2</v>
+        <v>-66.2</v>
       </c>
     </row>
     <row r="28">
@@ -3885,13 +3975,13 @@
         <v>413</v>
       </c>
       <c r="F30" t="n">
+        <v>314</v>
+      </c>
+      <c r="G30" t="n">
         <v>254</v>
       </c>
-      <c r="G30" t="n">
-        <v>252</v>
-      </c>
       <c r="H30" t="n">
-        <v>229</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31">
@@ -3910,13 +4000,13 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32">
@@ -3935,13 +4025,13 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33">
@@ -3966,7 +4056,7 @@
         <v>20</v>
       </c>
       <c r="H33" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -4010,13 +4100,13 @@
         <v>413</v>
       </c>
       <c r="F35" t="n">
-        <v>371</v>
+        <v>334</v>
       </c>
       <c r="G35" t="n">
-        <v>314</v>
+        <v>274</v>
       </c>
       <c r="H35" t="n">
-        <v>249</v>
+        <v>223</v>
       </c>
     </row>
     <row r="36">
@@ -4135,13 +4225,13 @@
         <v>494.6</v>
       </c>
       <c r="F40" t="n">
-        <v>437.4</v>
+        <v>400.4</v>
       </c>
       <c r="G40" t="n">
-        <v>365.2</v>
+        <v>325.2</v>
       </c>
       <c r="H40" t="n">
-        <v>285</v>
+        <v>259</v>
       </c>
     </row>
     <row r="41">
@@ -4313,10 +4403,10 @@
         <v>-180.4</v>
       </c>
       <c r="G47" t="n">
-        <v>-237.6</v>
+        <v>-274.6</v>
       </c>
       <c r="H47" t="n">
-        <v>-309.8</v>
+        <v>-349.8</v>
       </c>
     </row>
     <row r="48">
@@ -4335,13 +4425,13 @@
         <v>-94.2</v>
       </c>
       <c r="F48" t="n">
-        <v>-57.2</v>
+        <v>-94.2</v>
       </c>
       <c r="G48" t="n">
-        <v>-72.2</v>
+        <v>-75.2</v>
       </c>
       <c r="H48" t="n">
-        <v>-80.2</v>
+        <v>-66.2</v>
       </c>
     </row>
     <row r="49">
@@ -4360,13 +4450,13 @@
         <v>494.6</v>
       </c>
       <c r="F49" t="n">
-        <v>437.4</v>
+        <v>400.4</v>
       </c>
       <c r="G49" t="n">
-        <v>365.2</v>
+        <v>325.2</v>
       </c>
       <c r="H49" t="n">
-        <v>285</v>
+        <v>259</v>
       </c>
     </row>
     <row r="50">
@@ -4385,13 +4475,13 @@
         <v>494.6</v>
       </c>
       <c r="F50" t="n">
-        <v>437.4</v>
+        <v>400.4</v>
       </c>
       <c r="G50" t="n">
-        <v>365.2</v>
+        <v>325.2</v>
       </c>
       <c r="H50" t="n">
-        <v>285</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>
